--- a/out/LSTM_Base_repeat_3_000008.xlsx
+++ b/out/LSTM_Base_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.424137072939437</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.424137072939437</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.424137072939437</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.443559541701984</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.043559541701984</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001329268138119951</v>
+        <v>-8.814955669618211e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1527073781221157</v>
+        <v>-0.1012669099610395</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1529686908049362</v>
+        <v>-0.1014331470223259</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4616460895324502</v>
+        <v>0.280784626064627</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7712103801356526</v>
+        <v>0.4606757363498385</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03289222354012243</v>
+        <v>0.0200058822409753</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3746076923682177</v>
+        <v>0.2194519510909577</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05768175301434927</v>
+        <v>0.03508337270451147</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4570679979580026</v>
+        <v>0.2696063947709515</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07007651775146286</v>
+        <v>0.042622466309079</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5395337919971835</v>
+        <v>0.31976435981928</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01854383736495873</v>
+        <v>0.01127882762152322</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5064558101981972</v>
+        <v>0.2996452760272641</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01030228487552123</v>
+        <v>0.006264118489158451</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5084985040515894</v>
+        <v>0.3008857286902564</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02164512476753743</v>
+        <v>0.01316483409892891</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.443559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5415013381928825</v>
+        <v>0.320958103300164</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008501581137185028</v>
+        <v>0.005168706523071533</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5368387275952787</v>
+        <v>0.3181203424127828</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006052972194728778</v>
+        <v>0.003679461448730259</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.540439546427645</v>
+        <v>0.3203084030693702</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002379456945172864</v>
+        <v>0.001445227800367095</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.539140773329274</v>
+        <v>0.3195165296815226</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001348360760634314</v>
+        <v>0.0008181146311830566</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5394566484636504</v>
+        <v>0.3197066860844351</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005105480922692758</v>
+        <v>0.0003085565845920197</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5391283019845852</v>
+        <v>0.319505026608557</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002361103371081417</v>
+        <v>0.0001414277389743509</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5390907095545956</v>
+        <v>0.3194802041705244</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.380578237893718e-05</v>
+        <v>4.909079472171628e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5390209066411548</v>
+        <v>0.3194357333050648</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.123421634124512e-05</v>
+        <v>1.074052980474707e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5389794846789379</v>
+        <v>0.3194085493913081</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5389744645736029</v>
+        <v>0.3194035367323935</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5389704824890108</v>
+        <v>0.3193991551468328</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.53896804781882</v>
+        <v>0.3193958047920401</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5389625305768303</v>
+        <v>0.3193904354650522</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5389562065828224</v>
+        <v>0.3193844427316219</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.538950838794244</v>
+        <v>0.3193790749430435</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5389508755427357</v>
+        <v>0.3193791116915352</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5389509857882112</v>
+        <v>0.3193792219370107</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5389510592851948</v>
+        <v>0.3193792954339944</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.538951243027654</v>
+        <v>0.3193794791764535</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5389527864643104</v>
+        <v>0.31938102261311</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5389542564039835</v>
+        <v>0.3193824925527831</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5389555058527056</v>
+        <v>0.3193837420015051</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5389568655469029</v>
+        <v>0.3193851016957024</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5389546606373936</v>
+        <v>0.3193828967861931</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5389542564039835</v>
+        <v>0.3193824925527831</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5389534111886716</v>
+        <v>0.3193816473374712</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5389539624160489</v>
+        <v>0.3193821985648484</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5389536316796224</v>
+        <v>0.319381867828422</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.538953337691688</v>
+        <v>0.3193815738404875</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5389534111886716</v>
+        <v>0.3193816473374712</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5389529702067697</v>
+        <v>0.3193812063555692</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5389528599612941</v>
+        <v>0.3193810961100936</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5389528232128024</v>
+        <v>0.3193810593616019</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5389529702067697</v>
+        <v>0.3193812063555692</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.538952492476376</v>
+        <v>0.3193807286251755</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5389534479371633</v>
+        <v>0.3193816840859628</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5389534111886716</v>
+        <v>0.3193816473374712</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5389530804522452</v>
+        <v>0.3193813166010447</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5389535214341471</v>
+        <v>0.3193817575829467</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5389528967097861</v>
+        <v>0.3193811328585855</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5389527129673268</v>
+        <v>0.3193809491161264</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5389523087339169</v>
+        <v>0.3193805448827164</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5389514635186049</v>
+        <v>0.3193796996674044</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5389514267701132</v>
+        <v>0.3193796629189127</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5389515737640804</v>
+        <v>0.31937980991288</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5389515002670968</v>
+        <v>0.3193797364158963</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5389515737640804</v>
+        <v>0.31937980991288</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5389516105125723</v>
+        <v>0.3193798466613719</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5389515002670968</v>
+        <v>0.3193797364158963</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5389519412489987</v>
+        <v>0.3193801773977983</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5389518310035232</v>
+        <v>0.3193800671523228</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5389517942550313</v>
+        <v>0.3193800304038308</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5389517207580476</v>
+        <v>0.3193799569068472</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.538951684009556</v>
+        <v>0.3193799201583555</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5389514635186049</v>
+        <v>0.3193796996674044</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5389513900216213</v>
+        <v>0.3193796261704208</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5389513165246377</v>
+        <v>0.3193795526734372</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5389513532731296</v>
+        <v>0.3193795894219291</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.538951243027654</v>
+        <v>0.3193794791764535</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5389513532731296</v>
+        <v>0.3193795894219291</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.043559541701984</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.538951647261064</v>
+        <v>0.3193798834098636</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_3_000008.xlsx
+++ b/out/LSTM_Base_repeat_3_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975749</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204643</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.044636661902425</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.155363338097575</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204644</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204643</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242493</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.6108368500156143</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975751</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204643</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.443559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001329268138119951</v>
+        <v>-0.0001263585604768014</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1527073781221157</v>
+        <v>-0.1451617165892534</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.443559541701984</v>
+        <v>0.5001101738204642</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975752</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975751</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204643</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1528403049359277</v>
+        <v>-0.1452880751497303</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1529686908049362</v>
+        <v>-0.1454027727656553</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4616460895324502</v>
+        <v>0.4124262488151068</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7712103801356526</v>
+        <v>0.6802421128437007</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03289222354012243</v>
+        <v>0.02938528363674313</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3746076923682177</v>
+        <v>0.3259244133485616</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05768175301434927</v>
+        <v>0.05153190363197867</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4570679979580026</v>
+        <v>0.3995930572273154</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07007651775146286</v>
+        <v>0.06260486525679725</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204643</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5395337919971835</v>
+        <v>0.4732666049696805</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01854383736495873</v>
+        <v>0.01656698093725753</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.500110173820464</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5064558101981972</v>
+        <v>0.443715147381416</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01030228487552123</v>
+        <v>0.009203134653522236</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.443559541701984</v>
+        <v>0.500110173820464</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5084985040515894</v>
+        <v>0.4455395156133138</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02164512476753743</v>
+        <v>0.0193383865474902</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.443559541701984</v>
+        <v>1.155583685738504</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5415013381928825</v>
+        <v>0.4750241607531239</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008501581137185028</v>
+        <v>0.007594486992573471</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.043559541701984</v>
+        <v>0.5001101738204642</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5368387275952787</v>
+        <v>0.470858211650054</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006052972194728778</v>
+        <v>0.005406121519038774</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.1553633380975752</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.540439546427645</v>
+        <v>0.4740745272898544</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002379456945172864</v>
+        <v>0.002125531290988738</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.539140773329274</v>
+        <v>0.4729135307116402</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001348360760634314</v>
+        <v>0.001203467922935424</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5394566484636504</v>
+        <v>0.47319523621418</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005105480922692758</v>
+        <v>0.000455352738427235</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5391283019845852</v>
+        <v>0.4729011402103698</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002361103371081417</v>
+        <v>0.0002107882469095697</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5390907095545956</v>
+        <v>0.4728669630107875</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.380578237893718e-05</v>
+        <v>7.41178788466895e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5390209066411548</v>
+        <v>0.4728039355181507</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.123421634124512e-05</v>
+        <v>1.837230183129111e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5389794846789379</v>
+        <v>0.4727661561244766</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>6.924643791475056e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5389744645736029</v>
+        <v>0.4727611375084256</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5389704824890108</v>
+        <v>0.4727570467558385</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.53896804781882</v>
+        <v>0.4727544293524197</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5389625305768303</v>
+        <v>0.47274891211043</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5389562065828224</v>
+        <v>0.4727425881164221</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.538950838794244</v>
+        <v>0.4727372203278437</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5389508755427357</v>
+        <v>0.4727372570763353</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5389509857882112</v>
+        <v>0.4727373673218109</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.04463666190242488</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5389510592851948</v>
+        <v>0.4727374408187945</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204643</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.538951243027654</v>
+        <v>0.4727376245612537</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5389527864643104</v>
+        <v>0.4727391679979102</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5389542564039835</v>
+        <v>0.4727406379375833</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5389555058527056</v>
+        <v>0.4727418873863052</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5389568655469029</v>
+        <v>0.4727432470805026</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.043559541701984</v>
+        <v>0.7001101738204643</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5389546606373936</v>
+        <v>0.4727410421709933</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242481</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5389542564039835</v>
+        <v>0.4727406379375833</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5389534111886716</v>
+        <v>0.4727397927222713</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5389539624160489</v>
+        <v>0.4727403439496485</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5389536316796224</v>
+        <v>0.4727400132132221</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.538953337691688</v>
+        <v>0.4727397192252877</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5389534111886716</v>
+        <v>0.4727397927222713</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5389529702067697</v>
+        <v>0.4727393517403694</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5389528599612941</v>
+        <v>0.4727392414948938</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5389528232128024</v>
+        <v>0.4727392047464021</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5389529702067697</v>
+        <v>0.4727393517403694</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.04463666190242481</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.538952492476376</v>
+        <v>0.4727388740099757</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.043559541701984</v>
+        <v>0.04463666190242478</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5389534479371633</v>
+        <v>0.472739829470763</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8241370729394373</v>
+        <v>0.04463666190242478</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5389534111886716</v>
+        <v>0.4727397927222713</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8241370729394373</v>
+        <v>-0.6108368500156143</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5389530804522452</v>
+        <v>0.4727394619858449</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.6108368500156143</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5389535214341471</v>
+        <v>0.4727399029677468</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5389528967097861</v>
+        <v>0.4727392782433857</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5389527129673268</v>
+        <v>0.4727390945009265</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5389523087339169</v>
+        <v>0.4727386902675165</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5389514635186049</v>
+        <v>0.4727378450522046</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5389514267701132</v>
+        <v>0.4727378083037129</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5389515737640804</v>
+        <v>0.4727379552976801</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5389515002670968</v>
+        <v>0.4727378818006965</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5389515737640804</v>
+        <v>0.4727379552976801</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5389516105125723</v>
+        <v>0.472737992046172</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5389515002670968</v>
+        <v>0.4727378818006965</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5389519412489987</v>
+        <v>0.4727383227825984</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5389518310035232</v>
+        <v>0.4727382125371229</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5389517942550313</v>
+        <v>0.472738175788631</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5389517207580476</v>
+        <v>0.4727381022916474</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.538951684009556</v>
+        <v>0.4727380655431557</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5389514635186049</v>
+        <v>0.4727378450522046</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5389513900216213</v>
+        <v>0.472737771555221</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5389513165246377</v>
+        <v>0.4727376980582373</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.424137072939437</v>
+        <v>-0.8108368500156143</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5389513532731296</v>
+        <v>0.4727377348067293</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.424137072939437</v>
+        <v>0.04463666190242481</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.538951243027654</v>
+        <v>0.4727376245612537</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.043559541701984</v>
+        <v>0.700110173820464</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5389513532731296</v>
+        <v>0.4727377348067293</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.043559541701984</v>
+        <v>1.355583685738504</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.538951647261064</v>
+        <v>0.4727380287946637</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_3_000008.xlsx
+++ b/out/LSTM_Base_repeat_3_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.03982383385300636</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.02432911843061447</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.007791217416524887</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.1553633380975749</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.004032548516988754</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5001101738204643</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.0003272145986557007</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7001101738204644</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.005357168614864349</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.044636661902425</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.006773989647626877</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.00711638480424881</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.005163650959730148</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.004455350339412689</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.002602081745862961</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.001093599945306778</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0003735162317752838</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.155363338097575</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0001933574676513672</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.7001101738204644</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.003708779811859131</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001796606928110123</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.7001101738204643</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001160219311714172</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.04463666190242493</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.002428434789180756</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6108368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.002513818442821503</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.001964826136827469</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.001396313309669495</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.0006345249712467194</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.0001068376004695892</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1553633380975751</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001384250819683075</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.7001101738204643</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.001456946134567261</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0009168684482574463</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0003394968807697296</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0005934238433837891</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001632735133171082</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002842992544174194</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.009458087384700775</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.006280038505792618</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.355583685738504</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.00290948897600174</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.355583685738504</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001540675759315491</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0001929439604282379</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0008961483836174011</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.000657837837934494</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0004569105803966522</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002717535942792892</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.155583685738504</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.005315117537975311</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.155583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.005523409694433212</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.155583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.007673181593418121</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.155583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01311926171183586</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.155583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0170159786939621</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.155583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001263585604768014</v>
+        <v>-0.0001164229180378607</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1451617165892534</v>
+        <v>-0.1337475717430304</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.007156398147344589</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.155583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.001242358237504959</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5001101738204642</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.005231700837612152</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1553633380975752</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.007243882864713669</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.007597465068101883</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.006784357130527496</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.005260955542325974</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.002492781728506088</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0009148232638835907</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1553633380975751</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>8.550286293029785e-05</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7001101738204643</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.0004097260534763336</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.355583685738504</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.0004496648907661438</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.355583685738504</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.001605957746505737</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.355583685738504</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1452880751497303</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.006271399557590485</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.355583685738504</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1454027727656553</v>
+        <v>-0.1339602214965422</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4124262488151068</v>
+        <v>0.3460095288595149</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.003952786326408386</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.355583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6802421128437007</v>
+        <v>0.5587237016672185</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02938528363674313</v>
+        <v>0.02465314287075648</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.001814182847738266</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.355583685738504</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3259244133485616</v>
+        <v>0.2614649069697468</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05153190363197867</v>
+        <v>0.04323321274902012</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.003160152584314346</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.355583685738504</v>
+        <v>0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3995930572273154</v>
+        <v>0.32326996227078</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06260486525679725</v>
+        <v>0.05252293590161832</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>4.136934876441956e-05</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.7001101738204643</v>
+        <v>0.16</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4732666049696805</v>
+        <v>0.3850791318105855</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01656698093725753</v>
+        <v>0.01389904982514793</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.004879847168922424</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.500110173820464</v>
+        <v>0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.443715147381416</v>
+        <v>0.3602866133076321</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009203134653522236</v>
+        <v>0.00772023572250758</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.00225183367729187</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.500110173820464</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4455395156133138</v>
+        <v>0.3618163818401026</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0193383865474902</v>
+        <v>0.01622421290506169</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.007379598915576935</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.155583685738504</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4750241607531239</v>
+        <v>0.3865529418940516</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007594486992573471</v>
+        <v>0.006370091558391514</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.005139783024787903</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5001101738204642</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.470858211650054</v>
+        <v>0.3830570556072569</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005406121519038774</v>
+        <v>0.004535029275776237</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.001032840460538864</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1553633380975752</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4740745272898544</v>
+        <v>0.3857548807828361</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002125531290988738</v>
+        <v>0.001781984817680803</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.003821816295385361</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4729135307116402</v>
+        <v>0.3847799202469745</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001203467922935424</v>
+        <v>0.001009249863892231</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.007813882082700729</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.47319523621418</v>
+        <v>0.3850155776095018</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000455352738427235</v>
+        <v>0.0003813674768942865</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01117789000272751</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4729011402103698</v>
+        <v>0.3847678844033706</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002107882469095697</v>
+        <v>0.0001766584731636684</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01337257400155067</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4728669630107875</v>
+        <v>0.3847383838374074</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.41178788466895e-05</v>
+        <v>6.12006741370259e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01367918774485588</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4728039355181507</v>
+        <v>0.3846847822230896</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.837230183129111e-05</v>
+        <v>1.455641581801909e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01240070164203644</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4727661561244766</v>
+        <v>0.3846523005693743</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.924643791475056e-06</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01070938631892204</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4727611375084256</v>
+        <v>0.3846472849318916</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>1.369014529177619e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.006943218410015106</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4727570467558385</v>
+        <v>0.3846430487628176</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.006116636097431183</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4727544293524197</v>
+        <v>0.384640064883712</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.006134886294603348</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.47274891211043</v>
+        <v>0.3846346211387056</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.007079880684614182</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4727425881164221</v>
+        <v>0.3846286284052753</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.006460227072238922</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4727372203278437</v>
+        <v>0.3846232606166969</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.005802299827337265</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4727372570763353</v>
+        <v>0.3846232973651886</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.003829210996627808</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4727373673218109</v>
+        <v>0.3846234076106642</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003092482686042786</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.04463666190242488</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4727374408187945</v>
+        <v>0.3846234811076478</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.002583827823400497</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7001101738204643</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4727376245612537</v>
+        <v>0.3846236648501069</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01370209082961082</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.355583685738504</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4727391679979102</v>
+        <v>0.3846252082867634</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01666312664747238</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4727406379375833</v>
+        <v>0.3846266782264365</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01994322240352631</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4727418873863052</v>
+        <v>0.3846279276751585</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.03678884357213974</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.355583685738504</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4727432470805026</v>
+        <v>0.3846292873693558</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01357194781303406</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7001101738204643</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4727410421709933</v>
+        <v>0.3846270824598465</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.003721889108419418</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.04463666190242481</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4727406379375833</v>
+        <v>0.3846266782264365</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01590519770979881</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4727397927222713</v>
+        <v>0.3846258330111245</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02308428473770618</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4727403439496485</v>
+        <v>0.3846263842385018</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.02559372596442699</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4727400132132221</v>
+        <v>0.3846260535020753</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.02283124439418316</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4727397192252877</v>
+        <v>0.3846257595141409</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.02185449376702309</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4727397927222713</v>
+        <v>0.3846258330111245</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.02064051479101181</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4727393517403694</v>
+        <v>0.3846253920292226</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01880274154245853</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4727392414948938</v>
+        <v>0.384625281783747</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01480250805616379</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4727392047464021</v>
+        <v>0.3846252450352553</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.0137953907251358</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4727393517403694</v>
+        <v>0.3846253920292226</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.00409805029630661</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.04463666190242481</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4727388740099757</v>
+        <v>0.3846249142988289</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.003364399075508118</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.04463666190242478</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.472739829470763</v>
+        <v>0.3846258697596162</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.00570480152964592</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.04463666190242478</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4727397927222713</v>
+        <v>0.3846258330111245</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01212660223245621</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6108368500156143</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4727394619858449</v>
+        <v>0.3846255022746981</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01457079872488976</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6108368500156143</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4727399029677468</v>
+        <v>0.3846259432566</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01685817539691925</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4727392782433857</v>
+        <v>0.384625318532239</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01723306812345982</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4727390945009265</v>
+        <v>0.3846251347897798</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01863584853708744</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4727386902675165</v>
+        <v>0.3846247305563698</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01963589526712894</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4727378450522046</v>
+        <v>0.3846238853410578</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01712076552212238</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4727378083037129</v>
+        <v>0.3846238485925661</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01389843970537186</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4727379552976801</v>
+        <v>0.3846239955865333</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01106155663728714</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4727378818006965</v>
+        <v>0.3846239220895497</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003737125545740128</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4727379552976801</v>
+        <v>0.3846239955865333</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.006208054721355438</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.472737992046172</v>
+        <v>0.3846240323350252</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.004161488264799118</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4727378818006965</v>
+        <v>0.3846239220895497</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.005564097315073013</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4727383227825984</v>
+        <v>0.3846243630714516</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.005627274513244629</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4727382125371229</v>
+        <v>0.3846242528259761</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.007100850343704224</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.472738175788631</v>
+        <v>0.3846242160774842</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.007385876029729843</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4727381022916474</v>
+        <v>0.3846241425805006</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.007770266383886337</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4727380655431557</v>
+        <v>0.3846241058320089</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.008789341896772385</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.16</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4727378450522046</v>
+        <v>0.3846238853410578</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.007011361420154572</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8108368500156143</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.472737771555221</v>
+        <v>0.3846238118440742</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.006663281470537186</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4727376980582373</v>
+        <v>0.3846237383470906</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.006333474069833755</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8108368500156143</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4727377348067293</v>
+        <v>0.3846237750955825</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.004605453461408615</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.04463666190242481</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4727376245612537</v>
+        <v>0.3846236648501069</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>2.166256308555603e-05</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.700110173820464</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4727377348067293</v>
+        <v>0.3846237750955825</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.002007298171520233</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.355583685738504</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4727380287946637</v>
+        <v>0.3846240690835169</v>
       </c>
     </row>
   </sheetData>
